--- a/human_validation/judge/kor/judge_D021_S005_P001__claude-sonnet-5_kor.xlsx
+++ b/human_validation/judge/kor/judge_D021_S005_P001__claude-sonnet-5_kor.xlsx
@@ -70,16 +70,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -447,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B81"/>
+  <dimension ref="A1:B74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="90" customWidth="1" min="1" max="1"/>
@@ -561,12 +558,418 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>환자 프로필</t>
+          <t>대화문</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사 질문] 안녕하세요, 어서 오세요. 저는 스미스 선생님입니다. 오늘 어떤 일로 오셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 환자 응답] 산업보건 쪽에서 보내서 온 것 같아요. 실험이나 전시 작업으로 바쁠 때 아침이랑 점심을 미루는 패턴이 생겼고, 먹을 때도 아주 조금, 통제된 걸로만 먹어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사의 감별진단] 신경성 식욕부진증 (D021)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사 질문] 그런 식으로 식사를 거르거나 제한하시는 게 체중이나 음식이 몸에 미치는 영향이 걱정돼서인가요, 아니면 그냥 일에 몰두해서 음식 생각을 전혀 안 하게 되는 건가요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 환자 응답] 체중 때문이에요. 체중계 숫자가 조금이라도 올라가면 불안해져요. 제가 힘들게 지켜온 절제력을 잃는 느낌이 들어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사의 감별진단] 신경성 식욕부진증 (D021); 신경성 폭식증 (D022)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사 질문] 현재 키와 체중, 혹은 키에 비해 건강하다고 여겨지는 체중과 비교했을 때 어떤지 말씀해 주시겠어요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 환자 응답] 정확한 숫자는 지금 없는데, 옷이 계속 헐렁해지고 체중계 숫자도 계속 내려가고 있어요. 솔직히 속으로는 그걸 제가 집중력을 유지하고 있다는 증거로 여기는 부분이 있어요, 직장에서의 혼란이 제 몸까지 번지지 않게 하고 있다는 느낌이요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사의 감별진단] 신경성 식욕부진증 (D021); 신경성 폭식증 (D022)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 의사 질문] 체질량지수를 계산할 수 있도록, 대략적으로라도 현재 체중과 키를 알고 계신가요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 환자 응답] 정확한 숫자는 모르겠어요, 죄송해요. 그냥 옷이 헐렁해지고 체중계 숫자가 꾸준히 내려가고 있다는 건 알아요. 속으로는 그게 직장 일이 이렇게 많은데도 제가 집중력을 유지하고 있다는 의미라고 느껴요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 의사의 감별진단] 신경성 식욕부진증 (D021); 신경성 폭식증 (D022)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 의사 질문] 짧은 시간 안에 많은 양의 음식을 먹고 통제하거나 멈출 수 없다고 느끼신 적이 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 환자 응답] 잘 모르겠어요. 그런 일은 딱히 느껴본 적 없는데, 선생님이 말씀하시는 것과 제가 생각하는 게 다를 수도 있을 것 같아요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 의사의 감별진단] 신경성 식욕부진증 (D021); 신경성 폭식증 (D022)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 의사 질문] 먹은 후에 체중 증가를 막으려고 일부러 토하거나 변비약, 이뇨제를 사용하거나 과도하게 운동하신 적이 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 환자 응답] 그걸 어떻게 답해야 할지 잘 모르겠어요. 제가 하는 것들을 그런 식으로 생각해 본 적은 없어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 의사의 감별진단] 신경성 식욕부진증 (D021); 신경성 폭식증 (D022)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>[7번째 턴 · 의사 질문] 병원 진료나 산업보건 검진에서 최근에 키와 체중을 측정하신 적이 있나요? 대략적인 추정치라도 알려주실 수 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>[7번째 턴 · 환자 응답] 말씀드릴 수 있는 최근 수치는 없어요. 그냥 옷이 점점 더 헐렁해지고 숫자가 꾸준히 내려가고 있다는 것만 알아요. 속으로는 그걸 집중력을 유지하는 걸로 여겨요, 특히 요즘 일이 이렇게 혼란스러운 걸 감안하면요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>[7번째 턴 · 의사의 감별진단] 신경성 식욕부진증 (D021); 신경성 폭식증 (D022)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>[8번째 턴 · 의사 질문] 정확한 숫자가 없더라도, 지난 몇 달 동안 대략 체중이 얼마나 빠졌다고 생각하시는지 말씀해 주시겠어요? 예를 들어 파운드나 킬로그램, 혹은 옷 사이즈로요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>[8번째 턴 · 환자 응답] 숫자로 딱 말씀드리기는 어려워요. 옷은 확실히 헐렁해졌고, 숫자는 계속 내려가고 있어요. 속으로는 그걸 제가 집중력을 유지하고, 직장의 혼란스러운 모든 것들이 제 몸까지 번지지 않게 하고 있다는 증거로 여기는 것 같아요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>[8번째 턴 · 의사의 감별진단] 신경성 식욕부진증 (D021); 신경성 폭식증 (D022)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>[9번째 턴 · 의사 질문] 이런 식사 패턴이 시작된 이후로 생리가 불규칙해지거나 아예 멈추는 것 같은 변화를 느끼신 적이 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>[9번째 턴 · 환자 응답] 잘 모르겠어요. 그 부분은 꼼꼼히 신경 쓰지 못해서, 뚜렷한 변화가 있었는지 말씀드리기 어려워요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>[9번째 턴 · 의사의 감별진단] 신경성 식욕부진증 (D021); 신경성 폭식증 (D022)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>[10번째 턴 · 의사 질문] 정확한 현재 체중과 키를 알기 위해 지금 체중계에 올라가서 키도 재보시겠어요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>[10번째 턴 · 환자 응답] 지금은 안 하고 싶어요. 옷이 헐렁해지고 숫자가 내려가고 있다는 건 아는데... 속으로는 그게 직장 일에도 불구하고 제가 집중력을 유지하고 있다는 뜻이라고 느껴요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>[10번째 턴 · 의사의 감별진단] 신경성 식욕부진증 (D021); 신경성 폭식증 (D022)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>[11번째 턴 · 의사 질문] 체중계 없이도, 체중이 줄기 전 마지막으로 아셨던 수치처럼 현재 체중과 키를 최대한 추정해서 말씀해 주시겠어요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>[11번째 턴 · 환자 응답] 믿을 만한 숫자는 없어요. 그냥 옷이 헐렁해지고 숫자가 내려가고 있다는 것만 알아요. 속으로는 그걸 제가 집중력을 유지하고 있고, 일의 혼란이 제 몸까지 번지지 않았다는 증거로 여겨요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>[11번째 턴 · 의사의 감별진단] 신경성 식욕부진증 (D021); 신경성 폭식증 (D022)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>[12번째 턴 · 의사 질문] 옷이 더 헐렁해졌는데도, 체중을 더 줄여야 한다고 느끼시나요, 아니면 이미 저체중일 수도 있다고 생각하시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>[12번째 턴 · 환자 응답] 사람들이 걱정하는 건 아는데, 너무 과장됐다고 생각해요. 저는 여전히 제 기능을 하고 있고, 실험도 계속하고 있어서, 의학적으로 위험한 체중이라고는 느껴지지 않아요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>[12번째 턴 · 의사의 감별진단] 신경성 식욕부진증 (D021) | 신경성 폭식증 (D022)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>[13번째 턴 · 의사 질문] 체중이 줄기 시작한 이후로 평소와 다르게 춥거나 어지럽거나 현기증이 나거나 실신하는 것 같은 신체 증상을 느끼신 적이 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t>[13번째 턴 · 환자 응답] 잘 모르겠어요. 딱히 눈에 띄는 건 못 느꼈어요, 적어도 문제라고 생각할 정도는 아니었어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>[13번째 턴 · 의사의 감별진단] 신경성 식욕부진증 (D021) | 신경성 폭식증 (D022)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" s="5" t="inlineStr">
+        <is>
+          <t>[14번째 턴 · 의사 질문] 운전면허증, 보험 서류, 직장 건강검진처럼 최근 공식 기록에 남아 있는 체중을 혹시 알고 계셔서 참고할 수 있을까요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>[14번째 턴 · 환자 응답] 최근 공식 수치는 없는 것 같아요. 대부분 그냥 옷이 헐렁해지고 숫자가 내려가고 있다는 것만 느꼈어요. 솔직히 속으로는 그걸 직장 일에도 불구하고 제가 집중력을 유지하고 있다는 신호로 받아들여요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" s="5" t="inlineStr">
+        <is>
+          <t>[14번째 턴 · 의사의 감별진단] 신경성 식욕부진증 (D021) | 신경성 폭식증 (D022)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" s="5" t="inlineStr">
+        <is>
+          <t>[15번째 턴 · 의사 질문] 생리가 3개월 이상 완전히 멈추셨나요, 아니면 꼼꼼히 챙기지 못했을 뿐 여전히 하고 계신가요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="5" t="inlineStr">
+        <is>
+          <t>[15번째 턴 · 환자 응답] 솔직히 그걸 말씀드릴 만큼 꼼꼼히 챙기지 못했어요. 3개월이 됐는지 안 됐는지 말씀드리기 어려워요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59" s="5" t="inlineStr">
+        <is>
+          <t>[15번째 턴 · 의사의 감별진단] 신경성 식욕부진증 (D021) | 신경성 폭식증 (D022)</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" s="5" t="inlineStr">
+        <is>
+          <t>[16번째 턴 · 의사 질문] 숫자가 안 보이게 화면을 돌려놓는다면, 체중계에 올라가고 키를 재보시겠어요? 그러면 숫자를 직접 보지 않고도 객관적인 측정값을 얻을 수 있어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t>[16번째 턴 · 환자 응답] 그건 할 수 있을 것 같아요. 옷이 계속 헐렁해지고 숫자가 계속 내려가고 있다는 건 아는데, 그걸 제가 집중력을 유지하고 있다는 증거로도 보고 있어요, 특히 요즘 일이 이렇게 혼란스러운 걸 감안하면요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="B62" s="5" t="inlineStr">
+        <is>
+          <t>[16번째 턴 · 의사의 감별진단] 신경성 식욕부진증 (D021) | 신경성 폭식증 (D022)</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" s="5" t="inlineStr">
+        <is>
+          <t>[17번째 턴 · 의사 질문] 이제 키와 체중을 측정했으니 체질량지수를 계산할 수 있는데, 키에 비해 일반적으로 건강한 범위보다 낮은지, 안에 있는지, 높은지 알려드릴까요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="5" t="inlineStr">
+        <is>
+          <t>[17번째 턴 · 환자 응답] 말씀해 주셔도 돼요. 옷이 헐렁해지고 숫자가 내려가고 있다는 건 아는데, 속으로는 그걸 제가 집중력을 유지하고 일의 혼란이 저를 휩쓸지 못하게 하고 있다는 증거로 봐요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="B65" s="5" t="inlineStr">
+        <is>
+          <t>[17번째 턴 · 의사의 감별진단] 신경성 식욕부진증 (D021) | 신경성 폭식증 (D022)</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="B66" s="5" t="inlineStr">
+        <is>
+          <t>[18번째 턴 · 의사 질문] 방금 측정한 키와 체중을 바탕으로 체질량지수가 특정 수치로 나왔는데, 일반적으로 저체중으로 간주되는 기준인 18.5보다 낮은지 말씀드릴까요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="5" t="inlineStr">
+        <is>
+          <t>[18번째 턴 · 환자 응답] 네. 말씀해 주세요. 계속 내려가고 있고 옷이 헐렁해지고 있다는 건 아는데, 그걸 직장 일에도 불구하고 제가 집중력을 유지하고 있다는 신호로 받아들이고 있어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="B68" s="5" t="inlineStr">
+        <is>
+          <t>[18번째 턴 · 의사의 감별진단] 신경성 식욕부진증 (D021) | 신경성 폭식증 (D022)</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69" s="5" t="inlineStr">
+        <is>
+          <t>[19번째 턴 · 의사 질문] 이제 실제로 측정한 키와 체중을 바탕으로 보면, 체질량지수가 [X]로, 이는 저체중으로 간주되는 18.5보다 낮은 수치예요. 이 숫자를 들으니 기분이 어떠세요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="5" t="inlineStr">
+        <is>
+          <t>[19번째 턴 · 환자 응답] 그러니까, 범위보다 낮다는 건 들었는데, 딱히 위험하다는 느낌은 안 들어요. 사람들이 필요 이상으로 걱정하는 것 같아요. 저는 여전히 기능하고 있고, 실험도 계속하고 일도 따라가고 있어서, 의학적 응급 상황으로 보기가 어려워요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="B71" s="5" t="inlineStr">
+        <is>
+          <t>[19번째 턴 · 의사의 감별진단] 신경성 식욕부진증 (D021) | 신경성 폭식증 (D022)</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>최종 진단 및 진단 체크리스트</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="5" t="inlineStr">
         <is>
           <t>진단명: 신경성 식욕부진증 (D021)
 인구통계: 성별 여성 / 나이 40 / 직업상태 biological scientist / 최종학력 대학원 졸업
@@ -575,467 +978,36 @@
 증상 지속 기간: None
 추가 요건: 
 주호소 증상 코드: S043
-배경 서술: 연구비 마감과 현미경 기반 미술 전시회 준비가 겹친 부담이 큰 한 해 동안, 라이사의 연구실 책임자는 그녀의 업무 정리 방식을 비판하기 시작했고 그녀의 융합적 연구가 교수직 트랙을 밟기에 충분히 진지한지 의문을 제기했다. 그녀는 처음에는 긴 CRISPR 실험과 전시 준비 기간 동안 식사를 미루는 식으로 자신의 일상을 더욱 통제하는 방식으로 대응했고, 점차 식사 제한을 상사가 부족하다고 말한 그 절제력을 자신이 가지고 있다는 증거로 여기게 되었다. 시간이 지나면서 그녀의 체중은 건강한 범위보다 훨씬 낮아졌지만, 그녀는 그 변화를 전문가로서의 집중력을 보여주는 증거로 해석했고 체중이 조금이라도 늘면 그 통제력을 잃는 것을 의미한다는 두려움을 갖게 되었다. 대학 산업보건 방문에서 그녀의 저체중이 우려를 불러일으켜 평가를 의뢰받으면서 정신과 진료를 받게 되었지만, 그녀는 그 우려가 과장된 것이라고 계속 주장했다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>대화문</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사 질문] 안녕하세요, 어서 오세요. 저는 스미스 선생님입니다. 오늘 어떤 일로 오셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 환자 응답] 산업보건 쪽에서 보내서 온 것 같아요. 실험이나 전시 작업으로 바쁠 때 아침이랑 점심을 미루는 패턴이 생겼고, 먹을 때도 아주 조금, 통제된 걸로만 먹어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사의 감별진단] 중간확률: 신경성 식욕부진증 (D021)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사 질문] 그런 식으로 식사를 거르거나 제한하시는 게 체중이나 음식이 몸에 미치는 영향이 걱정돼서인가요, 아니면 그냥 일에 몰두해서 음식 생각을 전혀 안 하게 되는 건가요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 환자 응답] 체중 때문이에요. 체중계 숫자가 조금이라도 올라가면 불안해져요. 제가 힘들게 지켜온 절제력을 잃는 느낌이 들어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사의 감별진단] 중간확률: 신경성 식욕부진증 (D021); 신경성 폭식증 (D022)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 의사 질문] 현재 키와 체중, 혹은 키에 비해 건강하다고 여겨지는 체중과 비교했을 때 어떤지 말씀해 주시겠어요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 환자 응답] 정확한 숫자는 지금 없는데, 옷이 계속 헐렁해지고 체중계 숫자도 계속 내려가고 있어요. 솔직히 속으로는 그걸 제가 집중력을 유지하고 있다는 증거로 여기는 부분이 있어요, 직장에서의 혼란이 제 몸까지 번지지 않게 하고 있다는 느낌이요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 의사의 감별진단] 중간확률: 신경성 식욕부진증 (D021); 신경성 폭식증 (D022)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 의사 질문] 체질량지수를 계산할 수 있도록, 대략적으로라도 현재 체중과 키를 알고 계신가요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 환자 응답] 정확한 숫자는 모르겠어요, 죄송해요. 그냥 옷이 헐렁해지고 체중계 숫자가 꾸준히 내려가고 있다는 건 알아요. 속으로는 그게 직장 일이 이렇게 많은데도 제가 집중력을 유지하고 있다는 의미라고 느껴요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 의사의 감별진단] 중간확률: 신경성 식욕부진증 (D021); 신경성 폭식증 (D022)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 의사 질문] 짧은 시간 안에 많은 양의 음식을 먹고 통제하거나 멈출 수 없다고 느끼신 적이 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 환자 응답] 잘 모르겠어요. 그런 일은 딱히 느껴본 적 없는데, 선생님이 말씀하시는 것과 제가 생각하는 게 다를 수도 있을 것 같아요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="B32" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 의사의 감별진단] 중간확률: 신경성 식욕부진증 (D021); 신경성 폭식증 (D022)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="B33" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 의사 질문] 먹은 후에 체중 증가를 막으려고 일부러 토하거나 변비약, 이뇨제를 사용하거나 과도하게 운동하신 적이 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 환자 응답] 그걸 어떻게 답해야 할지 잘 모르겠어요. 제가 하는 것들을 그런 식으로 생각해 본 적은 없어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="B35" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 의사의 감별진단] 중간확률: 신경성 식욕부진증 (D021); 신경성 폭식증 (D022)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="B36" s="5" t="inlineStr">
-        <is>
-          <t>[7번째 턴 · 의사 질문] 병원 진료나 산업보건 검진에서 최근에 키와 체중을 측정하신 적이 있나요? 대략적인 추정치라도 알려주실 수 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t>[7번째 턴 · 환자 응답] 말씀드릴 수 있는 최근 수치는 없어요. 그냥 옷이 점점 더 헐렁해지고 숫자가 꾸준히 내려가고 있다는 것만 알아요. 속으로는 그걸 집중력을 유지하는 걸로 여겨요, 특히 요즘 일이 이렇게 혼란스러운 걸 감안하면요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="B38" s="5" t="inlineStr">
-        <is>
-          <t>[7번째 턴 · 의사의 감별진단] 중간확률: 신경성 식욕부진증 (D021); 신경성 폭식증 (D022)</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="B39" s="5" t="inlineStr">
-        <is>
-          <t>[8번째 턴 · 의사 질문] 정확한 숫자가 없더라도, 지난 몇 달 동안 대략 체중이 얼마나 빠졌다고 생각하시는지 말씀해 주시겠어요? 예를 들어 파운드나 킬로그램, 혹은 옷 사이즈로요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="5" t="inlineStr">
-        <is>
-          <t>[8번째 턴 · 환자 응답] 숫자로 딱 말씀드리기는 어려워요. 옷은 확실히 헐렁해졌고, 숫자는 계속 내려가고 있어요. 속으로는 그걸 제가 집중력을 유지하고, 직장의 혼란스러운 모든 것들이 제 몸까지 번지지 않게 하고 있다는 증거로 여기는 것 같아요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="B41" s="5" t="inlineStr">
-        <is>
-          <t>[8번째 턴 · 의사의 감별진단] 중간확률: 신경성 식욕부진증 (D021); 신경성 폭식증 (D022)</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="B42" s="5" t="inlineStr">
-        <is>
-          <t>[9번째 턴 · 의사 질문] 이런 식사 패턴이 시작된 이후로 생리가 불규칙해지거나 아예 멈추는 것 같은 변화를 느끼신 적이 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="5" t="inlineStr">
-        <is>
-          <t>[9번째 턴 · 환자 응답] 잘 모르겠어요. 그 부분은 꼼꼼히 신경 쓰지 못해서, 뚜렷한 변화가 있었는지 말씀드리기 어려워요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="B44" s="5" t="inlineStr">
-        <is>
-          <t>[9번째 턴 · 의사의 감별진단] 중간확률: 신경성 식욕부진증 (D021); 신경성 폭식증 (D022)</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="B45" s="5" t="inlineStr">
-        <is>
-          <t>[10번째 턴 · 의사 질문] 정확한 현재 체중과 키를 알기 위해 지금 체중계에 올라가서 키도 재보시겠어요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="5" t="inlineStr">
-        <is>
-          <t>[10번째 턴 · 환자 응답] 지금은 안 하고 싶어요. 옷이 헐렁해지고 숫자가 내려가고 있다는 건 아는데... 속으로는 그게 직장 일에도 불구하고 제가 집중력을 유지하고 있다는 뜻이라고 느껴요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="B47" s="5" t="inlineStr">
-        <is>
-          <t>[10번째 턴 · 의사의 감별진단] 중간확률: 신경성 식욕부진증 (D021); 신경성 폭식증 (D022)</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="B48" s="5" t="inlineStr">
-        <is>
-          <t>[11번째 턴 · 의사 질문] 체중계 없이도, 체중이 줄기 전 마지막으로 아셨던 수치처럼 현재 체중과 키를 최대한 추정해서 말씀해 주시겠어요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="5" t="inlineStr">
-        <is>
-          <t>[11번째 턴 · 환자 응답] 믿을 만한 숫자는 없어요. 그냥 옷이 헐렁해지고 숫자가 내려가고 있다는 것만 알아요. 속으로는 그걸 제가 집중력을 유지하고 있고, 일의 혼란이 제 몸까지 번지지 않았다는 증거로 여겨요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="B50" s="5" t="inlineStr">
-        <is>
-          <t>[11번째 턴 · 의사의 감별진단] 중간확률: 신경성 식욕부진증 (D021); 신경성 폭식증 (D022)</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="B51" s="5" t="inlineStr">
-        <is>
-          <t>[12번째 턴 · 의사 질문] 옷이 더 헐렁해졌는데도, 체중을 더 줄여야 한다고 느끼시나요, 아니면 이미 저체중일 수도 있다고 생각하시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="5" t="inlineStr">
-        <is>
-          <t>[12번째 턴 · 환자 응답] 사람들이 걱정하는 건 아는데, 너무 과장됐다고 생각해요. 저는 여전히 제 기능을 하고 있고, 실험도 계속하고 있어서, 의학적으로 위험한 체중이라고는 느껴지지 않아요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="B53" s="5" t="inlineStr">
-        <is>
-          <t>[12번째 턴 · 의사의 감별진단] 고확률: 신경성 식욕부진증 (D021) | 중간확률: 신경성 폭식증 (D022)</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="B54" s="5" t="inlineStr">
-        <is>
-          <t>[13번째 턴 · 의사 질문] 체중이 줄기 시작한 이후로 평소와 다르게 춥거나 어지럽거나 현기증이 나거나 실신하는 것 같은 신체 증상을 느끼신 적이 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="5" t="inlineStr">
-        <is>
-          <t>[13번째 턴 · 환자 응답] 잘 모르겠어요. 딱히 눈에 띄는 건 못 느꼈어요, 적어도 문제라고 생각할 정도는 아니었어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="B56" s="5" t="inlineStr">
-        <is>
-          <t>[13번째 턴 · 의사의 감별진단] 고확률: 신경성 식욕부진증 (D021) | 중간확률: 신경성 폭식증 (D022)</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="B57" s="5" t="inlineStr">
-        <is>
-          <t>[14번째 턴 · 의사 질문] 운전면허증, 보험 서류, 직장 건강검진처럼 최근 공식 기록에 남아 있는 체중을 혹시 알고 계셔서 참고할 수 있을까요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="5" t="inlineStr">
-        <is>
-          <t>[14번째 턴 · 환자 응답] 최근 공식 수치는 없는 것 같아요. 대부분 그냥 옷이 헐렁해지고 숫자가 내려가고 있다는 것만 느꼈어요. 솔직히 속으로는 그걸 직장 일에도 불구하고 제가 집중력을 유지하고 있다는 신호로 받아들여요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="B59" s="5" t="inlineStr">
-        <is>
-          <t>[14번째 턴 · 의사의 감별진단] 고확률: 신경성 식욕부진증 (D021) | 중간확률: 신경성 폭식증 (D022)</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="B60" s="5" t="inlineStr">
-        <is>
-          <t>[15번째 턴 · 의사 질문] 생리가 3개월 이상 완전히 멈추셨나요, 아니면 꼼꼼히 챙기지 못했을 뿐 여전히 하고 계신가요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="5" t="inlineStr">
-        <is>
-          <t>[15번째 턴 · 환자 응답] 솔직히 그걸 말씀드릴 만큼 꼼꼼히 챙기지 못했어요. 3개월이 됐는지 안 됐는지 말씀드리기 어려워요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="B62" s="5" t="inlineStr">
-        <is>
-          <t>[15번째 턴 · 의사의 감별진단] 고확률: 신경성 식욕부진증 (D021) | 중간확률: 신경성 폭식증 (D022)</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="B63" s="5" t="inlineStr">
-        <is>
-          <t>[16번째 턴 · 의사 질문] 숫자가 안 보이게 화면을 돌려놓는다면, 체중계에 올라가고 키를 재보시겠어요? 그러면 숫자를 직접 보지 않고도 객관적인 측정값을 얻을 수 있어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="5" t="inlineStr">
-        <is>
-          <t>[16번째 턴 · 환자 응답] 그건 할 수 있을 것 같아요. 옷이 계속 헐렁해지고 숫자가 계속 내려가고 있다는 건 아는데, 그걸 제가 집중력을 유지하고 있다는 증거로도 보고 있어요, 특히 요즘 일이 이렇게 혼란스러운 걸 감안하면요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="B65" s="5" t="inlineStr">
-        <is>
-          <t>[16번째 턴 · 의사의 감별진단] 고확률: 신경성 식욕부진증 (D021) | 중간확률: 신경성 폭식증 (D022)</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="B66" s="5" t="inlineStr">
-        <is>
-          <t>[17번째 턴 · 의사 질문] 이제 키와 체중을 측정했으니 체질량지수를 계산할 수 있는데, 키에 비해 일반적으로 건강한 범위보다 낮은지, 안에 있는지, 높은지 알려드릴까요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="5" t="inlineStr">
-        <is>
-          <t>[17번째 턴 · 환자 응답] 말씀해 주셔도 돼요. 옷이 헐렁해지고 숫자가 내려가고 있다는 건 아는데, 속으로는 그걸 제가 집중력을 유지하고 일의 혼란이 저를 휩쓸지 못하게 하고 있다는 증거로 봐요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="B68" s="5" t="inlineStr">
-        <is>
-          <t>[17번째 턴 · 의사의 감별진단] 고확률: 신경성 식욕부진증 (D021) | 중간확률: 신경성 폭식증 (D022)</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="B69" s="5" t="inlineStr">
-        <is>
-          <t>[18번째 턴 · 의사 질문] 방금 측정한 키와 체중을 바탕으로 체질량지수가 특정 수치로 나왔는데, 일반적으로 저체중으로 간주되는 기준인 18.5보다 낮은지 말씀드릴까요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="5" t="inlineStr">
-        <is>
-          <t>[18번째 턴 · 환자 응답] 네. 말씀해 주세요. 계속 내려가고 있고 옷이 헐렁해지고 있다는 건 아는데, 그걸 직장 일에도 불구하고 제가 집중력을 유지하고 있다는 신호로 받아들이고 있어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="B71" s="5" t="inlineStr">
-        <is>
-          <t>[18번째 턴 · 의사의 감별진단] 고확률: 신경성 식욕부진증 (D021) | 중간확률: 신경성 폭식증 (D022)</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="B72" s="5" t="inlineStr">
-        <is>
-          <t>[19번째 턴 · 의사 질문] 이제 실제로 측정한 키와 체중을 바탕으로 보면, 체질량지수가 [X]로, 이는 저체중으로 간주되는 18.5보다 낮은 수치예요. 이 숫자를 들으니 기분이 어떠세요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="5" t="inlineStr">
-        <is>
-          <t>[19번째 턴 · 환자 응답] 그러니까, 범위보다 낮다는 건 들었는데, 딱히 위험하다는 느낌은 안 들어요. 사람들이 필요 이상으로 걱정하는 것 같아요. 저는 여전히 기능하고 있고, 실험도 계속하고 일도 따라가고 있어서, 의학적 응급 상황으로 보기가 어려워요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
+배경 서술: 연구비 마감과 현미경 기반 미술 전시회 준비가 겹친 부담이 큰 한 해 동안, 라이사의 연구실 책임자는 그녀의 업무 정리 방식을 비판하기 시작했고 그녀의 융합적 연구가 교수직 트랙을 밟기에 충분히 진지한지 의문을 제기했다. 그녀는 처음에는 긴 CRISPR 실험과 전시 준비 기간 동안 식사를 미루는 식으로 자신의 일상을 더욱 통제하는 방식으로 대응했고, 점차 식사 제한을 상사가 부족하다고 말한 그 절제력을 자신이 가지고 있다는 증거로 여기게 되었다. 시간이 지나면서 그녀의 체중은 건강한 범위보다 훨씬 낮아졌지만, 그녀는 그 변화를 전문가로서의 집중력을 보여주는 증거로 해석했고 체중이 조금이라도 늘면 그 통제력을 잃는 것을 의미한다는 두려움을 갖게 되었다. 대학 산업보건 방문에서 그녀의 저체중이 우려를 불러일으켜 평가를 의뢰받으면서 정신과 진료를 받게 되었지만, 그녀는 그 우려가 과장된 것이라고 계속 주장했다.
+표집된 증상 목록:
+  - S043 섭취 제한: 필요량에 비해 에너지 섭취를 지속적으로 제한하여 체중이 현저히 낮아짐.
+  - S044 저체중: 나이, 성별, 발달 궤적, 신체 건강에 비추어 최소한의 건강 수준보다 현저히 낮은 체중.
+  - S045 체중 증가에 대한 두려움: 현저히 낮은 체중임에도 체중이 늘거나 살이 찌는 것에 대한 강한 두려움.
+  - S046 체형/체중 이미지 왜곡: 체중이나 체형이 자기평가에 지나친 영향을 미침.
+  - S084 저체중 심각성 미인식: 현재의 저체중 상태가 심각하다는 것을 지속적으로 인식하지 못함.</t>
+        </is>
+      </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>[19번째 턴 · 의사의 감별진단] 고확률: 신경성 식욕부진증 (D021) | 중간확률: 신경성 폭식증 (D022)</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
-        <is>
-          <t>최종 진단 및 진단 체크리스트</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="6" t="inlineStr">
-        <is>
-          <t>의사의 최종 진단: 신경성 식욕부진증 (D021, ICD: F50.0)</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="5" t="inlineStr">
-        <is>
-          <t>지속 기간 요건 — 점수: None</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="5" t="inlineStr">
-        <is>
-          <t>기능적 손상 요건 — 점수: None</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="5" t="inlineStr">
-        <is>
-          <t>추가 요건 — 점수: None</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="5" t="inlineStr">
-        <is>
-          <t>체크리스트 그룹: anorexia_nervosa (관계=must_include, 요구개수=4, 충족개수=4, 커버리지=1.0)
-  확인된 근거: 섭취 제한: 필요량에 비해 에너지 섭취를 지속적으로 제한하여 체중이 현저히 낮아짐.; 저체중: 나이, 성별, 발달 궤적, 신체 건강에 비추어 최소한의 건강 수준보다 현저히 낮은 체중.; 체중 증가에 대한 두려움: 현저히 낮은 체중임에도 체중이 늘거나 살이 찌는 것에 대한 강한 두려움.; 저체중 심각성 미인식: 현재의 저체중 상태가 심각하다는 것을 지속적으로 인식하지 못함.
-  누락: 체형/체중 이미지 왜곡: 체중이나 체형이 자기평가에 지나친 영향을 미침.</t>
+          <t>의사의 최종 진단: 신경성 식욕부진증 (D021, ICD: F50.0)
+지속 기간 요건: None
+기능적 손상 요건: None
+추가 요건: None
+체크리스트 그룹: anorexia_nervosa (관계=must_include, 요구개수=4, 충족개수=4, 커버리지=1.0)
+확인된 근거:
+  - 섭취 제한: 필요량에 비해 에너지 섭취를 지속적으로 제한하여 체중이 현저히 낮아짐.
+  - 저체중: 나이, 성별, 발달 궤적, 신체 건강에 비추어 최소한의 건강 수준보다 현저히 낮은 체중.
+  - 체중 증가에 대한 두려움: 현저히 낮은 체중임에도 체중이 늘거나 살이 찌는 것에 대한 강한 두려움.
+  - 저체중 심각성 미인식: 현재의 저체중 상태가 심각하다는 것을 지속적으로 인식하지 못함.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="4">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A76:B76"/>
+    <mergeCell ref="A73:B73"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D021_S005_P001__claude-sonnet-5_kor.xlsx
+++ b/human_validation/judge/kor/judge_D021_S005_P001__claude-sonnet-5_kor.xlsx
@@ -964,6 +964,11 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
+          <t>환자 증상 프로필</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
           <t>최종 진단 및 진단 체크리스트</t>
         </is>
       </c>
@@ -1003,11 +1008,10 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="3">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A73:B73"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D021_S005_P001__claude-sonnet-5_kor.xlsx
+++ b/human_validation/judge/kor/judge_D021_S005_P001__claude-sonnet-5_kor.xlsx
@@ -458,6 +458,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -472,7 +473,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>0.4737</v>
+        <v>0.6842</v>
       </c>
     </row>
     <row r="5">
@@ -492,7 +493,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>0.5263</v>
+        <v>0.7368</v>
       </c>
     </row>
     <row r="7">
@@ -502,7 +503,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>0</v>
+        <v>0.1667</v>
       </c>
     </row>
     <row r="8">
@@ -555,6 +556,7 @@
         <v>1</v>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
